--- a/4_model_training/4_0_model_versions.xlsx
+++ b/4_model_training/4_0_model_versions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Escritorio\UBA-CEIA\neural_profit\4_model_training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B5BAD5-9131-469B-93CC-67220359CC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755C2B41-D7BF-4A75-B44C-A306E35AD9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15615" yWindow="5280" windowWidth="8640" windowHeight="4425" xr2:uid="{6DF007C5-7310-47BD-AED1-A4F8B3F68C21}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6DF007C5-7310-47BD-AED1-A4F8B3F68C21}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -785,27 +785,15 @@
     <t>10–12</t>
   </si>
   <si>
-    <t>factor30, rsi_14, price_ema30, stoch_k_20, bb_percent_30_20, reversal_momentum_factor, rsi_7, reversal_media_factor, rsi_3, bb_percent_20_15</t>
-  </si>
-  <si>
     <t>12–15</t>
   </si>
   <si>
-    <t>factor30, rsi_14, price_ema30, stoch_k_20, bb_percent_30_20, reversal_momentum_factor, rsi_7, reversal_media_factor, rsi_3, momentum_3, reversion_vol_momentum_factor, roc_5, roc_20</t>
-  </si>
-  <si>
-    <t>igual que XGBoost, pero se pueden incluir también momentum_10 y atr_norm para aprovechar muchos features</t>
-  </si>
-  <si>
     <t>Árbol (maneja colinealidad)</t>
   </si>
   <si>
     <t>15 (casi todos)</t>
   </si>
   <si>
-    <t>factor30, rsi_14, price_ema30, stoch_k_20, bb_percent_30_20, reversal_momentum_factor, rsi_7, reversal_media_factor, rsi_3, bb_percent_20_15, momentum_3, reversion_vol_momentum_factor, roc_5, roc_20, momentum_10</t>
-  </si>
-  <si>
     <t>Red neuronal tabular</t>
   </si>
   <si>
@@ -818,9 +806,6 @@
     <t>Secuencial convolucional</t>
   </si>
   <si>
-    <t>factores con dinámicas rápidas: momentum_3, momentum_10, roc_5, roc_20, rsi_3, rsi_7, atr_norm, reversal_momentum_factor, reversion_vol_momentum_factor, price_ema30</t>
-  </si>
-  <si>
     <t>Secuencial atencional</t>
   </si>
   <si>
@@ -852,13 +837,53 @@
   </si>
   <si>
     <t>momentum_3, momentum_10, roc_5, roc_20, atr_norm, rsi_3, rsi_7, rsi_14, price_ema30, reversal_momentum_factor</t>
+  </si>
+  <si>
+    <t>factor30', 'rsi_14', 'price_ema30', 'stoch_k_20', 'bb_percent_30_20', 'reversal_momentum_factor', 'rsi_7', 'reversal_media_factor', 'rsi_3', 'bb_percent_20_15'</t>
+  </si>
+  <si>
+    <t>factor30', 'rsi_14', 'price_ema30', 'stoch_k_20', 'bb_percent_30_20', 'reversal_momentum_factor', 'rsi_7', 'reversal_media_factor', 'rsi_3', 'momentum_3', 'reversion_vol_momentum_factor', 'roc_5', 'roc_20'</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">igual que XGBoost, pero se pueden incluir también momentum_10 y atr_norm para aprovechar muchos features:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'factor30', 'rsi_14', 'price_ema30', 'stoch_k_20', 'bb_percent_30_20', 'reversal_momentum_factor', 'rsi_7', 'reversal_media_factor', 'rsi_3', 'momentum_3', 'reversion_vol_momentum_factor', 'roc_5', 'roc_20','momentum_10', 'atr_norm'</t>
+    </r>
+  </si>
+  <si>
+    <t>factor30', 'rsi_14', 'price_ema30', 'stoch_k_20', 'bb_percent_30_20', 'reversal_momentum_factor', 'rsi_7', 'reversal_media_factor', 'rsi_3', 'bb_percent_20_15', 'momentum_3', 'reversion_vol_momentum_factor', 'roc_5', 'roc_20', 'momentum_10'</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">factores con dinámicas rápidas: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'momentum_3', 'momentum_10', 'roc_5', 'roc_20', 'rsi_3', 'rsi_7', 'atr_norm', 'reversal_momentum_factor', 'reversion_vol_momentum_factor', 'price_ema30'</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -891,6 +916,13 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -931,7 +963,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -946,6 +978,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1350,8 +1385,8 @@
       <c r="H2" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>60</v>
+      <c r="I2" s="6" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -1377,13 +1412,13 @@
         <v>11</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -1406,10 +1441,10 @@
         <v>11</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -1417,7 +1452,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>22</v>
@@ -1435,10 +1470,10 @@
         <v>11</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -1446,7 +1481,7 @@
         <v>26</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>27</v>
@@ -1464,10 +1499,10 @@
         <v>11</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -1475,7 +1510,7 @@
         <v>29</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>30</v>
@@ -1496,7 +1531,7 @@
         <v>59</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -1504,7 +1539,7 @@
         <v>34</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>35</v>
@@ -1522,10 +1557,10 @@
         <v>33</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -1551,10 +1586,10 @@
         <v>11</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -1562,7 +1597,7 @@
         <v>42</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>43</v>
@@ -1583,7 +1618,7 @@
         <v>12</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -1591,7 +1626,7 @@
         <v>46</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>47</v>
@@ -1609,10 +1644,10 @@
         <v>33</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -1620,7 +1655,7 @@
         <v>50</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>51</v>
@@ -1641,7 +1676,7 @@
         <v>59</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
